--- a/data/valuebets_database_2025-07-31.xlsx
+++ b/data/valuebets_database_2025-07-31.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,10 +505,8 @@
           <t>08/08 18:30</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F2" t="n">
+        <v>60</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -521,7 +519,7 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>45869.08325205138</v>
+        <v>45869.08325204861</v>
       </c>
     </row>
     <row r="3">
@@ -550,10 +548,8 @@
           <t>04/08 19:00</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F3" t="n">
+        <v>55</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -566,7 +562,7 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>45869.08325205138</v>
+        <v>45869.08325204861</v>
       </c>
     </row>
     <row r="4">
@@ -595,10 +591,8 @@
           <t>03/08 13:00</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F4" t="n">
+        <v>55</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -611,7 +605,7 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>45869.08325205138</v>
+        <v>45869.08325204861</v>
       </c>
     </row>
     <row r="5">
@@ -640,10 +634,8 @@
           <t>08/08 18:45</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F5" t="n">
+        <v>45</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -656,7 +648,7 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>45869.08325205138</v>
+        <v>45869.08325204861</v>
       </c>
     </row>
     <row r="6">
@@ -685,10 +677,8 @@
           <t>09/08 00:00</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F6" t="n">
+        <v>50</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -701,7 +691,7 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>45869.08325205138</v>
+        <v>45869.08325204861</v>
       </c>
     </row>
     <row r="7">
@@ -730,10 +720,8 @@
           <t>31/07 16:10</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2.30</t>
-        </is>
+      <c r="F7" t="n">
+        <v>2.3</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -746,7 +734,7 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>45869.08325205138</v>
+        <v>45869.08325204861</v>
       </c>
     </row>
     <row r="8">
@@ -775,10 +763,8 @@
           <t>03/08 23:30</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F8" t="n">
+        <v>60</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -791,7 +777,7 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>45869.08325205138</v>
+        <v>45869.08325204861</v>
       </c>
     </row>
     <row r="9">
@@ -820,10 +806,8 @@
           <t>08/08 00:00</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F9" t="n">
+        <v>50</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -836,7 +820,7 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>45869.08325205138</v>
+        <v>45869.08325204861</v>
       </c>
     </row>
     <row r="10">
@@ -865,10 +849,8 @@
           <t>09/08 03:00</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F10" t="n">
+        <v>50</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -881,7 +863,7 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>45869.08325205138</v>
+        <v>45869.08325204861</v>
       </c>
     </row>
     <row r="11">
@@ -910,10 +892,8 @@
           <t>31/07 16:30</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>1.60</t>
-        </is>
+      <c r="F11" t="n">
+        <v>1.6</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -926,7 +906,7 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>45869.08325205138</v>
+        <v>45869.08325204861</v>
       </c>
     </row>
     <row r="12">
@@ -955,10 +935,8 @@
           <t>09/08 17:30</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F12" t="n">
+        <v>45</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -971,7 +949,7 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>45869.08325205138</v>
+        <v>45869.08325204861</v>
       </c>
     </row>
     <row r="13">
@@ -1000,10 +978,8 @@
           <t>03/08 19:00</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F13" t="n">
+        <v>55</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1016,7 +992,7 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>45869.08325205138</v>
+        <v>45869.08325204861</v>
       </c>
     </row>
     <row r="14">
@@ -1045,10 +1021,8 @@
           <t>31/07 19:00</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F14" t="n">
+        <v>45</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1061,7 +1035,7 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>45869.08325205138</v>
+        <v>45869.08325204861</v>
       </c>
     </row>
     <row r="15">
@@ -1090,10 +1064,8 @@
           <t>02/08 18:00</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F15" t="n">
+        <v>45</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1106,7 +1078,7 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>45869.08325205138</v>
+        <v>45869.08325204861</v>
       </c>
     </row>
     <row r="16">
@@ -1135,10 +1107,8 @@
           <t>31/07 19:00</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F16" t="n">
+        <v>40</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1151,7 +1121,7 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>45869.08325205138</v>
+        <v>45869.08325204861</v>
       </c>
     </row>
     <row r="17">
@@ -1180,10 +1150,8 @@
           <t>09/08 18:30</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F17" t="n">
+        <v>50</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1196,7 +1164,7 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>45869.08325205138</v>
+        <v>45869.08325204861</v>
       </c>
     </row>
     <row r="18">
@@ -1225,10 +1193,8 @@
           <t>31/07 16:30</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F18" t="n">
+        <v>45</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1241,7 +1207,7 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>45869.08325205138</v>
+        <v>45869.08325204861</v>
       </c>
     </row>
     <row r="19">
@@ -1270,10 +1236,8 @@
           <t>03/08 19:00</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F19" t="n">
+        <v>45</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1286,7 +1250,7 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>45869.08325205138</v>
+        <v>45869.08325204861</v>
       </c>
     </row>
     <row r="20">
@@ -1315,10 +1279,8 @@
           <t>31/07 23:10</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
+      <c r="F20" t="n">
+        <v>5</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1331,7 +1293,7 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>45869.08325205138</v>
+        <v>45869.08325204861</v>
       </c>
     </row>
     <row r="21">
@@ -1360,10 +1322,8 @@
           <t>03/08 17:00</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F21" t="n">
+        <v>45</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1376,7 +1336,7 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>45869.08325205138</v>
+        <v>45869.08325204861</v>
       </c>
     </row>
     <row r="22">
@@ -1405,10 +1365,8 @@
           <t>31/07 23:00</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>1.50</t>
-        </is>
+      <c r="F22" t="n">
+        <v>1.5</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1421,7 +1379,7 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>45869.08325205138</v>
+        <v>45869.08325204861</v>
       </c>
     </row>
     <row r="23">
@@ -1450,10 +1408,8 @@
           <t>01/08 00:10</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2.45</t>
-        </is>
+      <c r="F23" t="n">
+        <v>2.45</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1466,7 +1422,7 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>45869.08325205138</v>
+        <v>45869.08325204861</v>
       </c>
     </row>
     <row r="24">
@@ -1495,10 +1451,8 @@
           <t>04/08 01:30</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F24" t="n">
+        <v>40</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1511,7 +1465,7 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>45869.08325205138</v>
+        <v>45869.08325204861</v>
       </c>
     </row>
     <row r="25">
@@ -1540,10 +1494,8 @@
           <t>02/08 18:30</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F25" t="n">
+        <v>50</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1556,7 +1508,7 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>45869.08325205138</v>
+        <v>45869.08325204861</v>
       </c>
     </row>
     <row r="26">
@@ -1585,10 +1537,8 @@
           <t>31/07 23:00</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>1.42</t>
-        </is>
+      <c r="F26" t="n">
+        <v>1.42</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1601,7 +1551,187 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>45869.08325205138</v>
+        <v>45869.08325204861</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Lokomotiva</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Lokomotiva Zagreb – HNK Vukovar 1991HNL</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>01/08 18:00</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2,33%</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>+4,99%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>45869.15712611654</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Boca Junio</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Boca Juniors – Racing ClubLiga Profesional</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>09/08 19:30</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>40.00</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2,58%</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>+3,15%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>45869.15712611654</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Tennis | Tie-break: Oui | Karen Khac</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Karen Khachanov – Emilio NavaToronto ATP</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Tie-break: Oui</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>31/07 15:00</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>41,3%</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>+3,13%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>45869.15712611654</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football | 1 | Fortuna Du</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Fortuna Dusseldorf – Hanovre 96Allemagne - 2. Bundesliga A9ZJ2X7R 385076e7</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>09/08 11:00</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>46,8%</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>+2,99%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>45869.15712611654</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-31.xlsx
+++ b/data/valuebets_database_2025-07-31.xlsx
@@ -1580,10 +1580,8 @@
           <t>01/08 18:00</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F27" t="n">
+        <v>45</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1596,7 +1594,7 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>45869.15712611654</v>
+        <v>45869.15712611111</v>
       </c>
     </row>
     <row r="28">
@@ -1625,10 +1623,8 @@
           <t>09/08 19:30</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F28" t="n">
+        <v>40</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1641,7 +1637,7 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>45869.15712611654</v>
+        <v>45869.15712611111</v>
       </c>
     </row>
     <row r="29">
@@ -1670,10 +1666,8 @@
           <t>31/07 15:00</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
+      <c r="F29" t="n">
+        <v>2.5</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1686,7 +1680,7 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>45869.15712611654</v>
+        <v>45869.15712611111</v>
       </c>
     </row>
     <row r="30">
@@ -1715,10 +1709,8 @@
           <t>09/08 11:00</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>2.20</t>
-        </is>
+      <c r="F30" t="n">
+        <v>2.2</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1731,7 +1723,7 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>45869.15712611654</v>
+        <v>45869.15712611111</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-31.xlsx
+++ b/data/valuebets_database_2025-07-31.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I30"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1726,6 +1726,141 @@
         <v>45869.15712611111</v>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ParionsSport(FR)Tennis | 1 - aces | L.Musetti </t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>L.Musetti – A.MichelsenATP - Toronto</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>1 - aces</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>31/07 16:30</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>31,1%</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>+8,85%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>45869.27505432085</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Basketball | X3e période[race to 15 regular time] | Golden Sta</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Basketball</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Golden State Valkyries – Washington MysticsUSA - WNBA</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>X3e période[race to 15 regular time]</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>31/07 23:30</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>25.00</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>4,29%</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>+7,31%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>45869.27505432085</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Winamax(FR)Football | 21-2- se qualifie | Utrecht – </t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Utrecht – Sheriff TiraspolEurope - Ligue Europa</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>21-2- se qualifie</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>31/07 18:00</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>2,13%</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>+6,28%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>45869.27505432085</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-07-31.xlsx
+++ b/data/valuebets_database_2025-07-31.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1752,10 +1752,8 @@
           <t>31/07 16:30</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
+      <c r="F31" t="n">
+        <v>3.5</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1768,7 +1766,7 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>45869.27505432085</v>
+        <v>45869.27505431713</v>
       </c>
     </row>
     <row r="32">
@@ -1797,10 +1795,8 @@
           <t>31/07 23:30</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>25.00</t>
-        </is>
+      <c r="F32" t="n">
+        <v>25</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1813,7 +1809,7 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>45869.27505432085</v>
+        <v>45869.27505431713</v>
       </c>
     </row>
     <row r="33">
@@ -1842,10 +1838,8 @@
           <t>31/07 18:00</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F33" t="n">
+        <v>50</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1858,7 +1852,97 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>45869.27505432085</v>
+        <v>45869.27505431713</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Football | Plus que 3.52e équipe | Cukaricki </t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Cukaricki – Radnicki NisSuperLiga</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>03/08 17:00</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>40.00</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>2,87%</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>+14,9%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>45869.31039624778</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>PMU(FR)Football | 1 | Tukums 200</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>PMU(FR)Football</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Tukums 2000 – FC RigaLettonie. Lettonie - Virsliga</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>03/08 15:00</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>24.00</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>4,56%</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>+9,35%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>45869.31039624778</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-31.xlsx
+++ b/data/valuebets_database_2025-07-31.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I35"/>
+  <dimension ref="A1:I36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1881,10 +1881,8 @@
           <t>03/08 17:00</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F34" t="n">
+        <v>40</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1897,7 +1895,7 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>45869.31039624778</v>
+        <v>45869.31039625</v>
       </c>
     </row>
     <row r="35">
@@ -1926,10 +1924,8 @@
           <t>03/08 15:00</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>24.00</t>
-        </is>
+      <c r="F35" t="n">
+        <v>24</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1942,7 +1938,52 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>45869.31039624778</v>
+        <v>45869.31039625</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Colorado R</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Colorado Rapids – Santos LagunaLeagues Cup</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>01/08 01:30</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>2,37%</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>+6,43%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>45869.35643652847</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-31.xlsx
+++ b/data/valuebets_database_2025-07-31.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I36"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1967,10 +1967,8 @@
           <t>01/08 01:30</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F36" t="n">
+        <v>45</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1983,7 +1981,232 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>45869.35643652847</v>
+        <v>45869.35643652778</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 10.5 - tirs2e équipe | Häcken – A</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Häcken – AnderlechtEurope - Ligue Europa</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Moins que 10.5 - tirs2e équipe</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>31/07 17:00</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2.53</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>47,9%</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>+21,2%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>45869.39568692573</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Tennis | Tie-break: Oui | Amanda Ani</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Amanda Anisimova – Emma RaducanuMontreal WTA</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Tie-break: Oui</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>01/08 16:30</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>28,8%</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>+15,2%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>45869.39568692573</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | San Lorenz</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>San Lorenzo – Velez SarsfieldLiga Profesional</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>07/08 22:00</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>2,24%</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>+12,1%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>45869.39568692573</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 1.5 - tir cadré2e équipe | Sporting B</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Sporting Braga – Levski SofiaEurope - Ligue Europa</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Moins que 1.5 - tir cadré2e équipe</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>31/07 19:00</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>31,9%</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>+8,48%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>45869.39568692573</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Basketball | H 1 (−1.5)4e période | Côte d'Ivo</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Basketball</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Côte d'Ivoire (F) – Sénégal (F)International - Afrobasket (F)</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>H 1 (−1.5)4e période</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>31/07 18:00</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>43,3%</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>+3,92%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>45869.39568692573</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-31.xlsx
+++ b/data/valuebets_database_2025-07-31.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I41"/>
+  <dimension ref="A1:I43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2010,10 +2010,8 @@
           <t>31/07 17:00</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>2.53</t>
-        </is>
+      <c r="F37" t="n">
+        <v>2.53</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -2026,7 +2024,7 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>45869.39568692573</v>
+        <v>45869.3956869213</v>
       </c>
     </row>
     <row r="38">
@@ -2055,10 +2053,8 @@
           <t>01/08 16:30</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
+      <c r="F38" t="n">
+        <v>4</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -2071,7 +2067,7 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>45869.39568692573</v>
+        <v>45869.3956869213</v>
       </c>
     </row>
     <row r="39">
@@ -2100,10 +2096,8 @@
           <t>07/08 22:00</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F39" t="n">
+        <v>50</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -2116,7 +2110,7 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>45869.39568692573</v>
+        <v>45869.3956869213</v>
       </c>
     </row>
     <row r="40">
@@ -2145,10 +2139,8 @@
           <t>31/07 19:00</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
+      <c r="F40" t="n">
+        <v>3.4</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -2161,7 +2153,7 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>45869.39568692573</v>
+        <v>45869.3956869213</v>
       </c>
     </row>
     <row r="41">
@@ -2190,10 +2182,8 @@
           <t>31/07 18:00</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>2.40</t>
-        </is>
+      <c r="F41" t="n">
+        <v>2.4</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -2206,7 +2196,97 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>45869.39568692573</v>
+        <v>45869.3956869213</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis | 2 - aces | Lorenzo Mu</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Lorenzo Musetti – Alex MichelsenATP - Toronto</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2 - aces</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>31/07 16:30</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>63,1%</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>+13,7%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>45869.43542447102</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 2.5 - tir cadré2e équipe | Legia Vars</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Legia Varsovie – Banik OstravaEurope - Ligue Europa</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Moins que 2.5 - tir cadré2e équipe</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>31/07 19:00</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2.58</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>41,5%</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>+7,14%</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>45869.43542447102</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-31.xlsx
+++ b/data/valuebets_database_2025-07-31.xlsx
@@ -2225,10 +2225,8 @@
           <t>31/07 16:30</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
+      <c r="F42" t="n">
+        <v>1.8</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2241,7 +2239,7 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>45869.43542447102</v>
+        <v>45869.43542446759</v>
       </c>
     </row>
     <row r="43">
@@ -2270,10 +2268,8 @@
           <t>31/07 19:00</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>2.58</t>
-        </is>
+      <c r="F43" t="n">
+        <v>2.58</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2286,7 +2282,7 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>45869.43542447102</v>
+        <v>45869.43542446759</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-31.xlsx
+++ b/data/valuebets_database_2025-07-31.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I43"/>
+  <dimension ref="A1:I48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2285,6 +2285,231 @@
         <v>45869.43542446759</v>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 12.5 - tirs1re équipe | Häcken – A</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Häcken – AnderlechtEurope - Ligue Europa</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Plus que 12.5 - tirs1re équipe</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>31/07 17:00</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>57,3%</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>+8,92%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>45869.53503220069</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 2.5 - tir cadré2e équipe | Sporting B</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Sporting Braga – Levski SofiaEurope - Ligue Europa</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Moins que 2.5 - tir cadré2e équipe</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>31/07 19:00</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>56,8%</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>+4,99%</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>45869.53503220069</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis | Plus que 5.51er set2e participant | Coco Gauff</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Coco Gauff – Veronika KudermetovaWTA 1000 Montreal</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Plus que 5.51er set2e participant</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>31/07 17:40</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2.85</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>36,4%</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>+3,61%</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>45869.53503220069</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 11.5 - tirs2e équipe | Shakhtar D</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Shakhtar Donetsk – BesiktasEurope - Ligue Europa</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Plus que 11.5 - tirs2e équipe</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>31/07 18:00</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>58,2%</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>+3,60%</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>45869.53503220069</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Football | Moins que 14.5 - tirs2e équipe | Hibernian </t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Hibernian – FC MidtjyllandEurope - Ligue Europa</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Moins que 14.5 - tirs2e équipe</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>31/07 19:00</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2.37</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>43,5%</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>+3,04%</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>45869.53503220069</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-07-31.xlsx
+++ b/data/valuebets_database_2025-07-31.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I48"/>
+  <dimension ref="A1:I49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2311,10 +2311,8 @@
           <t>31/07 17:00</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>1.90</t>
-        </is>
+      <c r="F44" t="n">
+        <v>1.9</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2327,7 +2325,7 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>45869.53503220069</v>
+        <v>45869.53503219908</v>
       </c>
     </row>
     <row r="45">
@@ -2356,10 +2354,8 @@
           <t>31/07 19:00</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
+      <c r="F45" t="n">
+        <v>1.85</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2372,7 +2368,7 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>45869.53503220069</v>
+        <v>45869.53503219908</v>
       </c>
     </row>
     <row r="46">
@@ -2401,10 +2397,8 @@
           <t>31/07 17:40</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>2.85</t>
-        </is>
+      <c r="F46" t="n">
+        <v>2.85</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2417,7 +2411,7 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>45869.53503220069</v>
+        <v>45869.53503219908</v>
       </c>
     </row>
     <row r="47">
@@ -2446,10 +2440,8 @@
           <t>31/07 18:00</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>1.78</t>
-        </is>
+      <c r="F47" t="n">
+        <v>1.78</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2462,7 +2454,7 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>45869.53503220069</v>
+        <v>45869.53503219908</v>
       </c>
     </row>
     <row r="48">
@@ -2491,10 +2483,8 @@
           <t>31/07 19:00</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>2.37</t>
-        </is>
+      <c r="F48" t="n">
+        <v>2.37</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2507,7 +2497,52 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>45869.53503220069</v>
+        <v>45869.53503219908</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>PMU(FR)Football | 2 | AZ Alkmaar</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>PMU(FR)Football</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>AZ Alkmaar – Ilves TampereEurope. Europa Conférence (Q)</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>31/07 16:45</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>20.00</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>5,29%</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>+5,78%</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>45869.5697614103</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-31.xlsx
+++ b/data/valuebets_database_2025-07-31.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I49"/>
+  <dimension ref="A1:I52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2526,10 +2526,8 @@
           <t>31/07 16:45</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>20.00</t>
-        </is>
+      <c r="F49" t="n">
+        <v>20</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2542,7 +2540,142 @@
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>45869.5697614103</v>
+        <v>45869.56976141204</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>PMU(FR)Tennis | Moins que 8.51er set | Khachanov,</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>PMU(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Khachanov, Karen – Nava, EmilioEvénements. ATP Toronto</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Moins que 8.51er set</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>31/07 15:00</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>5.40</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>20,5%</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>+10,5%</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>45869.60068176621</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis | Plus que 5.51er set2e participant | Mirra Andr</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Mirra Andreeva – McCartney KesslerWTA 1000 Montreal</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Plus que 5.51er set2e participant</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>31/07 18:00</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>38,4%</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>+3,55%</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="n">
+        <v>45869.60068176621</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis | Plus que 6.51er set2e participant | Learner Ti</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Learner Tien – Reilly OpelkaATP 1000 Toronto</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Plus que 6.51er set2e participant</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>31/07 21:00</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>5.20</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>19,8%</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>+3,00%</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="n">
+        <v>45869.60068176621</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-31.xlsx
+++ b/data/valuebets_database_2025-07-31.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I52"/>
+  <dimension ref="A1:I53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2569,10 +2569,8 @@
           <t>31/07 15:00</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>5.40</t>
-        </is>
+      <c r="F50" t="n">
+        <v>5.4</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2585,7 +2583,7 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>45869.60068176621</v>
+        <v>45869.60068177083</v>
       </c>
     </row>
     <row r="51">
@@ -2614,10 +2612,8 @@
           <t>31/07 18:00</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>2.70</t>
-        </is>
+      <c r="F51" t="n">
+        <v>2.7</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2630,7 +2626,7 @@
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>45869.60068176621</v>
+        <v>45869.60068177083</v>
       </c>
     </row>
     <row r="52">
@@ -2659,10 +2655,8 @@
           <t>31/07 21:00</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>5.20</t>
-        </is>
+      <c r="F52" t="n">
+        <v>5.2</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2675,7 +2669,52 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>45869.60068176621</v>
+        <v>45869.60068177083</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.51re équipe | Ceara SC –</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Ceara SC – FlamengoSérie A</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>03/08 21:30</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>1,94%</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>+16,2%</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="n">
+        <v>45869.64330279389</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-31.xlsx
+++ b/data/valuebets_database_2025-07-31.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I53"/>
+  <dimension ref="A1:I55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2698,10 +2698,8 @@
           <t>03/08 21:30</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F53" t="n">
+        <v>60</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2714,7 +2712,97 @@
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>45869.64330279389</v>
+        <v>45869.64330278935</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Football | Pas de buts | AZ – Ilves</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Football</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>AZ – IlvesLigue Europa Conférence - Éliminatoires</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>31/07 16:45</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>41.00</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>2,52%</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>+3,48%</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="n">
+        <v>45869.68819548724</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis | Plus que 6.51er set2e participant | Brandon Na</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Brandon Nakashima – Ben SheltonATP 1000 Toronto</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Plus que 6.51er set2e participant</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>01/08 15:00</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>23,0%</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>+3,31%</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="n">
+        <v>45869.68819548724</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-31.xlsx
+++ b/data/valuebets_database_2025-07-31.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:I60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2741,10 +2741,8 @@
           <t>31/07 16:45</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>41.00</t>
-        </is>
+      <c r="F54" t="n">
+        <v>41</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2757,7 +2755,7 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>45869.68819548724</v>
+        <v>45869.68819548611</v>
       </c>
     </row>
     <row r="55">
@@ -2786,10 +2784,8 @@
           <t>01/08 15:00</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
+      <c r="F55" t="n">
+        <v>4.5</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2802,7 +2798,232 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>45869.68819548724</v>
+        <v>45869.68819548611</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Football | Plus que 3.52e équipe | Utrecht – </t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Utrecht – FC Sheriff TiraspolLigue Europa</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>31/07 18:00</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>65.00</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>2,17%</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>+40,7%</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="n">
+        <v>45869.7241482797</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football | Moins que 12.5 - tirs1re équipe | CFR Cluj –</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>CFR Cluj – FC LuganoEurope - Ligue Europa</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Moins que 12.5 - tirs1re équipe</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>31/07 17:30</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>55,8%</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>+6,06%</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="n">
+        <v>45869.7241482797</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis | Moins que 5.51er set1er participant | Coco Gauff</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Coco Gauff – Veronika KudermetovaWTA 1000 Montreal</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Moins que 5.51er set1er participant</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>31/07 17:40</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>25,2%</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>+5,95%</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="n">
+        <v>45869.7241482797</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PokerStars(FR)Football | Pas de buts | Brondby – </t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Football</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Brondby – HB TorshavnLigue Europa Conférence - Éliminatoires</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>31/07 17:30</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>46.00</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>2,27%</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>+4,59%</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="n">
+        <v>45869.7241482797</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Mirassol F</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Mirassol FC SP – Vasco da GamaSérie A</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>02/08 21:30</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>2,30%</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>+3,41%</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="n">
+        <v>45869.7241482797</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-31.xlsx
+++ b/data/valuebets_database_2025-07-31.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I60"/>
+  <dimension ref="A1:I68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2827,10 +2827,8 @@
           <t>31/07 18:00</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>65.00</t>
-        </is>
+      <c r="F56" t="n">
+        <v>65</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2843,7 +2841,7 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>45869.7241482797</v>
+        <v>45869.72414827546</v>
       </c>
     </row>
     <row r="57">
@@ -2872,10 +2870,8 @@
           <t>31/07 17:30</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>1.90</t>
-        </is>
+      <c r="F57" t="n">
+        <v>1.9</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2888,7 +2884,7 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>45869.7241482797</v>
+        <v>45869.72414827546</v>
       </c>
     </row>
     <row r="58">
@@ -2917,10 +2913,8 @@
           <t>31/07 17:40</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
+      <c r="F58" t="n">
+        <v>4.2</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2933,7 +2927,7 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>45869.7241482797</v>
+        <v>45869.72414827546</v>
       </c>
     </row>
     <row r="59">
@@ -2962,10 +2956,8 @@
           <t>31/07 17:30</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>46.00</t>
-        </is>
+      <c r="F59" t="n">
+        <v>46</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2978,7 +2970,7 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>45869.7241482797</v>
+        <v>45869.72414827546</v>
       </c>
     </row>
     <row r="60">
@@ -3007,10 +2999,8 @@
           <t>02/08 21:30</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F60" t="n">
+        <v>45</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -3023,7 +3013,367 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>45869.7241482797</v>
+        <v>45869.72414827546</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis | 2 - aces | A.Rublev –</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>A.Rublev – L.SonegoATP - Toronto</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>2 - aces</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>01/08 15:00</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>47,9%</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>+31,6%</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="n">
+        <v>45869.77457801764</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis | 1 - aces | A.Fils – J</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>A.Fils – J.LeheckaATP - Toronto</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>1 - aces</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>01/08 15:00</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>50,0%</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>+24,9%</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="n">
+        <v>45869.77457801764</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Barracas C</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Barracas Central – CA AldosiviLiga Profesional</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>10/08 18:00</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>2,50%</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>+24,9%</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="n">
+        <v>45869.77457801764</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis | 2 - aces | A.Sevastov</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>A.Sevastova – J.PegulaWTA - Montreal F</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>2 - aces</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>01/08 16:30</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>69,3%</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>+17,9%</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="n">
+        <v>45869.77457801764</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis | 1 - aces | G.Diallo –</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>G.Diallo – T.FritzATP - Toronto</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>1 - aces</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>01/08 15:00</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>28,0%</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>+12,1%</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="n">
+        <v>45869.77457801764</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis | 2 - aces | F.Tiafoe –</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>F.Tiafoe – A.VukicATP - Toronto</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>2 - aces</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>01/08 15:00</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>79,8%</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>+11,7%</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="n">
+        <v>45869.77457801764</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis | 2 - aces | B.Bencic –</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>B.Bencic – K.MuchovaWTA - Montreal F</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>2 - aces</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>01/08 16:30</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>1.20</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>89,5%</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>+7,40%</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="n">
+        <v>45869.77457801764</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PMU(FR)Football | 11-2- se qualifie | Dungannon </t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>PMU(FR)Football</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Dungannon Swifts – FC VaduzEurope. Europa Conférence (Q)</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>11-2- se qualifie</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>31/07 18:45</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>49,9%</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>+4,84%</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="n">
+        <v>45869.77457801764</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-31.xlsx
+++ b/data/valuebets_database_2025-07-31.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I68"/>
+  <dimension ref="A1:I69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3042,10 +3042,8 @@
           <t>01/08 15:00</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
+      <c r="F61" t="n">
+        <v>2.75</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -3058,7 +3056,7 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>45869.77457801764</v>
+        <v>45869.77457802084</v>
       </c>
     </row>
     <row r="62">
@@ -3087,10 +3085,8 @@
           <t>01/08 15:00</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
+      <c r="F62" t="n">
+        <v>2.5</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -3103,7 +3099,7 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>45869.77457801764</v>
+        <v>45869.77457802084</v>
       </c>
     </row>
     <row r="63">
@@ -3132,10 +3128,8 @@
           <t>10/08 18:00</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F63" t="n">
+        <v>50</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -3148,7 +3142,7 @@
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>45869.77457801764</v>
+        <v>45869.77457802084</v>
       </c>
     </row>
     <row r="64">
@@ -3177,10 +3171,8 @@
           <t>01/08 16:30</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>1.70</t>
-        </is>
+      <c r="F64" t="n">
+        <v>1.7</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -3193,7 +3185,7 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>45869.77457801764</v>
+        <v>45869.77457802084</v>
       </c>
     </row>
     <row r="65">
@@ -3222,10 +3214,8 @@
           <t>01/08 15:00</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
+      <c r="F65" t="n">
+        <v>4</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -3238,7 +3228,7 @@
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>45869.77457801764</v>
+        <v>45869.77457802084</v>
       </c>
     </row>
     <row r="66">
@@ -3267,10 +3257,8 @@
           <t>01/08 15:00</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>1.40</t>
-        </is>
+      <c r="F66" t="n">
+        <v>1.4</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -3283,7 +3271,7 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>45869.77457801764</v>
+        <v>45869.77457802084</v>
       </c>
     </row>
     <row r="67">
@@ -3312,10 +3300,8 @@
           <t>01/08 16:30</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>1.20</t>
-        </is>
+      <c r="F67" t="n">
+        <v>1.2</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -3328,7 +3314,7 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>45869.77457801764</v>
+        <v>45869.77457802084</v>
       </c>
     </row>
     <row r="68">
@@ -3357,10 +3343,8 @@
           <t>31/07 18:45</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
+      <c r="F68" t="n">
+        <v>2.1</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -3373,7 +3357,52 @@
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>45869.77457801764</v>
+        <v>45869.77457802084</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football | Moins que 22.5 - tirs | Sporting P</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Sporting Portugal – BenficaPortugal - Super Coupe</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Moins que 22.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>31/07 19:45</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>38,6%</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>+8,03%</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="n">
+        <v>45869.80570812837</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-31.xlsx
+++ b/data/valuebets_database_2025-07-31.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I69"/>
+  <dimension ref="A1:I72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3386,10 +3386,8 @@
           <t>31/07 19:45</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>2.80</t>
-        </is>
+      <c r="F69" t="n">
+        <v>2.8</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -3402,7 +3400,142 @@
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>45869.80570812837</v>
+        <v>45869.805708125</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Football | Plus que 3.52e équipe | Instituto </t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Instituto AC Cordoba – CA PlatenseLiga Profesional</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>10/08 20:00</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>2,45%</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>+22,6%</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="n">
+        <v>45869.85222306912</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis | Moins que 3.5 - break | Andrey Rub</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Andrey Rublev – Lorenzo SonegoATP - Toronto</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Moins que 3.5 - break</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>01/08 16:30</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>49,0%</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>+2,99%</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="n">
+        <v>45869.85222306912</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Winamax(FR)Tennis | Moins que 3.5 - break | Alexander </t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Alexander Zverev – Matteo ArnaldiATP - Toronto</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Moins que 3.5 - break</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>31/07 23:00</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>46,7%</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>+2,69%</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="n">
+        <v>45869.85222306912</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-31.xlsx
+++ b/data/valuebets_database_2025-07-31.xlsx
@@ -3429,10 +3429,8 @@
           <t>10/08 20:00</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F70" t="n">
+        <v>50</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -3445,7 +3443,7 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>45869.85222306912</v>
+        <v>45869.85222306713</v>
       </c>
     </row>
     <row r="71">
@@ -3474,10 +3472,8 @@
           <t>01/08 16:30</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
+      <c r="F71" t="n">
+        <v>2.1</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -3490,7 +3486,7 @@
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>45869.85222306912</v>
+        <v>45869.85222306713</v>
       </c>
     </row>
     <row r="72">
@@ -3519,10 +3515,8 @@
           <t>31/07 23:00</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>2.20</t>
-        </is>
+      <c r="F72" t="n">
+        <v>2.2</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -3535,7 +3529,7 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>45869.85222306912</v>
+        <v>45869.85222306713</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-31.xlsx
+++ b/data/valuebets_database_2025-07-31.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I72"/>
+  <dimension ref="A1:I73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3532,6 +3532,51 @@
         <v>45869.85222306713</v>
       </c>
     </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.51re équipe | Sportivo A</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Sportivo Ameliano – Libertad AsuncionPrimera Division</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>04/08 19:00</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>2,89%</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>+29,9%</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="n">
+        <v>45869.93305102355</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-07-31.xlsx
+++ b/data/valuebets_database_2025-07-31.xlsx
@@ -3558,10 +3558,8 @@
           <t>04/08 19:00</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F73" t="n">
+        <v>45</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -3574,7 +3572,7 @@
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>45869.93305102355</v>
+        <v>45869.93305101852</v>
       </c>
     </row>
   </sheetData>
